--- a/semester 2/BI/BBCA.JK_2021-01-01_2022-12-31.xlsx
+++ b/semester 2/BI/BBCA.JK_2021-01-01_2022-12-31.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adi\Documents\GitHub\thesiss2\semester 2\BI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATA ARSIP\IJAZAH KOMPUTERKU\THESIS\thesiss2\semester 2\BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29374BE5-068B-438E-8555-4053C39D04F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0B6966-4B4B-476B-BD53-A5D20C01FF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1566,6 +1566,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-FBBB-4D87-8496-A6AB8F162FF8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1585,6 +1590,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-FBBB-4D87-8496-A6AB8F162FF8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1604,6 +1614,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-FBBB-4D87-8496-A6AB8F162FF8}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>

--- a/semester 2/BI/BBCA.JK_2021-01-01_2022-12-31.xlsx
+++ b/semester 2/BI/BBCA.JK_2021-01-01_2022-12-31.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adi\Documents\GitHub\thesiss2\semester 2\BI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATA ARSIP\IJAZAH KOMPUTERKU\THESIS\thesiss2\semester 2\BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78672EB-1A68-486C-953A-D4C8395695FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CB112E-7AE8-471E-8A44-64B07546ADE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -296,10 +296,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -38567,7 +38563,7 @@
       <c r="J7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -38717,7 +38713,7 @@
       <c r="J12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -39109,18 +39105,18 @@
     </row>
     <row r="33" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="6">
         <f>COUNTIF(mei_23,"Naik")</f>
         <v>7</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="6">
         <f>COUNTIF(mei_23,"Turun")</f>
         <v>8</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="6">
         <f>COUNTIF(mei_23,"Stabil")</f>
         <v>6</v>
       </c>
@@ -39199,18 +39195,18 @@
     </row>
     <row r="38" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="6">
         <f>COUNTIF(okt_23,"Naik")</f>
         <v>9</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="6">
         <f>COUNTIF(okt_23,"Turun")</f>
         <v>11</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="6">
         <f>COUNTIF(okt_23,"Stabil")</f>
         <v>2</v>
       </c>

--- a/semester 2/BI/BBCA.JK_2021-01-01_2022-12-31.xlsx
+++ b/semester 2/BI/BBCA.JK_2021-01-01_2022-12-31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DATA ARSIP\IJAZAH KOMPUTERKU\THESIS\thesiss2\semester 2\BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605D9BB6-5174-4B67-B88A-619E586136A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F7CE1A-AAA6-477C-BAB4-45B9921A63FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,6 +329,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-ID"/>
+              <a:t>Data</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-ID" baseline="0"/>
+              <a:t> saham Bank BCA</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -667,6 +697,7544 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Close vs Volume</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Close vs Volume</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$1206</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1205"/>
+                <c:pt idx="0">
+                  <c:v>6028.375</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6253.28173828125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6125.39306640625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6143.03271484375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6218.001953125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6478.18701171875</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6315.01953125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6279.7412109375</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6191.5419921875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6134.21240234375</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6279.7412109375</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6257.6904296875</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6257.6904296875</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6240.0517578125</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6244.4619140625</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6204.77197265625</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6015.14453125</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5988.68505859375</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6085.7041015625</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5962.2255859375</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6015.14453125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5997.505859375</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6019.5546875</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6046.013671875</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6098.93359375</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6103.34326171875</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6156.263671875</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6103.34326171875</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6068.064453125</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5997.505859375</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6120.9833984375</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6085.7041015625</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5940.17626953125</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6019.5546875</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5988.68505859375</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6019.5546875</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5931.35546875</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5913.71630859375</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5918.12646484375</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6213.59130859375</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6187.1328125</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6173.90283203125</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5926.9453125</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5997.505859375</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5926.9453125</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5825.51806640625</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5913.71630859375</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5966.63623046875</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5878.43701171875</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5843.1572265625</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5829.92822265625</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5913.71630859375</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5962.2255859375</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5838.7470703125</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5790.23876953125</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5679.98974609375</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5618.2509765625</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5657.94091796875</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5609.43115234375</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5640.30126953125</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5481.54296875</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5490.36376953125</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5428.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5437.443359375</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5512.412109375</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5486.83447265625</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5544.96728515625</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5424.22998046875</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5366.0966796875</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5638.87353515625</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5616.51513671875</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5612.04345703125</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5607.5712890625</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5576.26953125</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5513.6650390625</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5558.38232421875</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5714.89306640625</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5620.986328125</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5728.30859375</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5652.28857421875</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5732.78076171875</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5728.30859375</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5714.89306640625</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5723.8369140625</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5746.1953125</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5746.1953125</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5723.8369140625</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5741.72412109375</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5795.384765625</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5813.271484375</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5714.89306640625</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5674.64794921875</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5705.94921875</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5688.0625</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5656.7607421875</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5683.59228515625</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5607.5712890625</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5670.17578125</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5701.47802734375</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5781.9697265625</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5884.8193359375</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5840.1025390625</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5750.66845703125</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5840.1025390625</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5920.59326171875</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5786.44189453125</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5732.78076171875</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5786.44189453125</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5710.42138671875</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5661.232421875</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5656.7607421875</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5589.68505859375</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5670.17578125</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5571.7978515625</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5553.9111328125</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5536.0234375</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5415.2861328125</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5406.34326171875</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5388.4560546875</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5388.4560546875</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5455.53173828125</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5464.4755859375</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5415.2861328125</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5424.22998046875</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5379.51171875</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5383.98388671875</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5518.13720703125</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5406.34326171875</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5357.15380859375</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>5468.94677734375</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5464.4755859375</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5370.56884765625</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5375.041015625</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5504.72119140625</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5397.39892578125</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5370.56884765625</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5370.56884765625</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5348.2099609375</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5401.87109375</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5339.26708984375</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5330.32275390625</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5495.7783203125</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5473.41943359375</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5634.40185546875</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>5509.193359375</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5544.96728515625</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5634.40185546875</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5634.40185546875</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>5732.78076171875</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5741.72412109375</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>5893.76318359375</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5866.93310546875</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5822.2158203125</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5871.40478515625</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5857.98974609375</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5871.40478515625</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>5849.04638671875</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5902.70654296875</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5880.3486328125</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5875.876953125</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>5759.61083984375</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>5875.876953125</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5831.1591796875</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>5862.46142578125</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>5853.517578125</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>5808.80029296875</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>5813.271484375</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5831.1591796875</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5889.2919921875</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5804.32861328125</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5862.46142578125</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>5884.8193359375</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5889.2919921875</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5884.8193359375</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5831.1591796875</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5884.8193359375</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>6260.44677734375</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>6045.802734375</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6224.6728515625</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>6211.25732421875</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>6421.43017578125</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>6403.54296875</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>6519.80810546875</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>6488.505859375</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>6546.63818359375</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>6729.98095703125</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>6931.20849609375</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>6841.77392578125</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>6729.98095703125</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>6707.6220703125</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>6618.1865234375</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>6729.98095703125</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>6729.98095703125</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>6729.98095703125</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>6662.904296875</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>6595.8271484375</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>6685.2626953125</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>6618.1865234375</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>6528.75146484375</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>6573.46923828125</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>6595.8271484375</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>6662.904296875</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>6774.69775390625</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>6864.13232421875</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>6841.77392578125</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>6864.13232421875</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>6729.98095703125</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>6707.6220703125</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>6685.2626953125</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>6797.43115234375</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>6640.3955078125</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>6662.82958984375</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>6707.6962890625</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>6707.6962890625</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>6707.6962890625</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>6662.82958984375</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>6528.22607421875</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>6640.3955078125</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>6528.22607421875</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>6730.13037109375</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>6617.96142578125</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>6595.52783203125</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>6595.52783203125</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>6662.82958984375</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>6595.52783203125</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>6617.96142578125</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>6528.22607421875</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>6730.13037109375</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>6617.96142578125</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>6617.96142578125</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>6573.09375</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>6595.52783203125</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>6595.52783203125</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>6550.65966796875</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>6573.09375</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>6640.3955078125</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>6685.2626953125</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>6707.6962890625</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>6864.732421875</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>6819.86474609375</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>6909.60009765625</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>6909.60009765625</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>6909.60009765625</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>7044.20361328125</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>6954.4677734375</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>6887.16748046875</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>6887.16748046875</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>6976.90087890625</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>7133.9375</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>6999.3349609375</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>6976.90087890625</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>6909.60009765625</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>6999.3349609375</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>6976.90087890625</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>6842.298828125</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>6999.3349609375</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>6932.0341796875</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>6932.0341796875</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>6999.3349609375</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>6932.0341796875</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>7133.9375</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>6954.4677734375</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>7021.76904296875</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>6909.60009765625</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>7066.63671875</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>7156.37158203125</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>7089.07080078125</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>7111.50390625</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>7133.9375</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>7089.07080078125</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>7223.67333984375</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>7178.80517578125</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>7223.67333984375</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>7223.67333984375</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>7156.37158203125</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>7089.07080078125</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>6909.60009765625</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>6864.732421875</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>7044.20361328125</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>7111.50390625</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>7133.9375</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>7246.107421875</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>7313.40771484375</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>7358.27587890625</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>7178.80517578125</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>7089.07080078125</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>7089.07080078125</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>7111.50390625</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>7089.07080078125</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>7111.50390625</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>7133.9375</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>7152.16064453125</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>7174.93798828125</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>7266.0478515625</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>7220.49267578125</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>7061.04931640625</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>7061.04931640625</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>7152.16064453125</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>7038.27197265625</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>7106.60498046875</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>7106.60498046875</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>7015.494140625</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>7015.494140625</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>6947.16162109375</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>6969.93896484375</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>7220.49267578125</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>7174.93798828125</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>7288.8251953125</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>7402.71337890625</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>7471.04638671875</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>7402.71337890625</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>6924.38427734375</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>6856.0517578125</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>6969.93896484375</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>6628.275390625</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>6673.8310546875</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>6742.16357421875</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>6901.60595703125</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>6787.71923828125</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>6742.16357421875</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>6719.38623046875</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>6696.6083984375</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>6719.38623046875</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>6901.60595703125</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>6901.60595703125</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>7061.04931640625</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>6901.60595703125</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>6924.38427734375</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>6787.71923828125</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>6719.38623046875</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>6924.38427734375</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>6833.27392578125</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>6696.6083984375</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>6696.6083984375</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>6742.16357421875</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>6673.8310546875</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>6901.60595703125</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>6833.27392578125</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>6947.16162109375</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>6969.93896484375</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>6833.27392578125</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>6856.0517578125</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>6810.49609375</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>6696.6083984375</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>6651.05322265625</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>6628.275390625</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>6605.4990234375</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>6605.4990234375</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>6423.27734375</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>6605.4990234375</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>6651.05322265625</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>6468.83251953125</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>6514.38818359375</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>6491.60986328125</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>6537.1650390625</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>6377.72216796875</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>6400.5</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>6377.72216796875</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>6514.38818359375</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>6537.1650390625</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>6742.16357421875</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>6742.16357421875</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>6673.8310546875</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>6651.05322265625</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>6651.05322265625</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>6673.8310546875</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>6696.6083984375</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>6696.6083984375</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>6833.27392578125</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>6924.38427734375</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>6947.16162109375</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>7106.60498046875</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>7174.93798828125</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>7174.93798828125</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>7243.27001953125</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>7220.49267578125</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>7243.27001953125</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>7266.0478515625</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>7288.8251953125</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>7288.8251953125</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>7197.71533203125</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>7243.27001953125</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>7357.15869140625</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>7288.8251953125</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>7425.49072265625</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>7448.2685546875</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>7471.04638671875</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>7425.49072265625</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>7493.82373046875</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>7539.37939453125</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>7539.37939453125</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>7630.4892578125</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>7607.7119140625</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>7630.4892578125</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>7630.4892578125</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>7767.15478515625</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>7744.37646484375</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>7972.15283203125</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>7698.82177734375</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>7881.04248046875</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>7789.931640625</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>7721.599609375</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>7721.599609375</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>7630.4892578125</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>7676.044921875</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>7562.15625</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>7584.93408203125</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>7630.4892578125</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>7789.931640625</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>7744.37646484375</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>7789.931640625</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>7698.82177734375</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>7676.044921875</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>7471.04638671875</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>7562.15625</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>7516.60205078125</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>7584.93408203125</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>7539.37939453125</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>7516.60205078125</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>7516.60205078125</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>7562.15625</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>7539.37939453125</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>7744.37646484375</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>7881.04248046875</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>8108.81787109375</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>7926.59814453125</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>7789.931640625</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>7926.59814453125</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>7972.15283203125</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>8017.70849609375</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>8017.70849609375</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>7972.15283203125</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>8017.70849609375</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>7994.93017578125</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>8063.2626953125</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>7972.15283203125</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>8086.0419921875</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>8017.70849609375</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>8063.2626953125</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>7972.15283203125</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>8017.70849609375</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>7835.4873046875</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>7949.375</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>8040.4853515625</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>7949.375</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>8108.81787109375</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>8086.0419921875</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>8199.9287109375</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>8177.150390625</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>8222.7060546875</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>8177.150390625</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>8473.259765625</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>8199.9287109375</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>8140.4755859375</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>8026.14306640625</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>7934.67724609375</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>7728.87841796875</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>7774.611328125</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>7888.94482421875</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>7774.611328125</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>7866.078125</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>7911.81103515625</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>7934.67724609375</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>7774.611328125</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>7866.078125</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>7911.81103515625</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>7820.34423828125</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>7820.34423828125</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>7820.34423828125</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>7637.4130859375</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>7545.947265625</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>7591.6796875</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>7728.87841796875</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>7477.34716796875</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>7431.6142578125</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>7477.34716796875</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>7363.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>7454.48046875</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>7614.5458984375</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>7591.6796875</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>7614.5458984375</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>7591.6796875</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>7523.080078125</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>7500.2138671875</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>7751.74560546875</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>7751.74560546875</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>7774.611328125</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>7728.87841796875</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>7980.41015625</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>8094.7421875</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>8071.87646484375</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>8140.4755859375</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>8071.87646484375</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>8117.61083984375</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>8186.208984375</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>8117.61083984375</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>7980.41015625</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>8003.27685546875</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>7934.67724609375</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>7980.41015625</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>7934.67724609375</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>8026.14306640625</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>8003.27685546875</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>7866.078125</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>7888.94482421875</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>7751.74560546875</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>7683.14599609375</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>7706.0126953125</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>7843.21142578125</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>7728.87841796875</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>7820.34423828125</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>7614.5458984375</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>7614.5458984375</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>7591.6796875</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>7660.279296875</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>7683.14599609375</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>7774.611328125</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>8071.87646484375</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>7957.54443359375</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>7934.67724609375</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>8209.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>8233.21875</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>8163.248046875</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>8209.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>8186.572265625</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>8139.92431640625</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>8163.248046875</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>8209.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>8233.21875</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>8303.1884765625</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>8419.8076171875</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>8233.21875</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>8209.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>8186.572265625</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>8116.6015625</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>8186.572265625</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>8419.8076171875</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>8629.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>8489.779296875</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>8489.779296875</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>8419.8076171875</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>8419.8076171875</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>8559.748046875</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>8559.748046875</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>8489.779296875</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>8723.0126953125</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>8606.396484375</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>8629.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>8653.04296875</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>8769.66015625</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>8769.66015625</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>8769.66015625</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>8723.0126953125</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>8676.3671875</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>8676.3671875</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>8629.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>8559.748046875</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>8676.3671875</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>8676.3671875</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>8653.04296875</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>8629.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>8559.748046875</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>8606.396484375</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>8606.396484375</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>8606.396484375</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>8559.748046875</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>8489.779296875</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>8489.779296875</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>8536.42578125</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>8513.1005859375</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>8349.8359375</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>8233.21875</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>8583.0732421875</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>8419.8076171875</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>8489.779296875</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>8349.8359375</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>8256.5419921875</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>8163.248046875</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>8373.16015625</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>8256.5419921875</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>8186.572265625</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>8139.92431640625</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>8116.6015625</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>8256.5419921875</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>8163.248046875</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>8023.30712890625</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>8256.5419921875</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>8303.1884765625</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>8373.16015625</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>8396.484375</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>8233.21875</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>8443.130859375</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>8466.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>8186.572265625</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>8326.513671875</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>8279.8662109375</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>8303.1884765625</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>8373.16015625</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>8349.8359375</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>8366.240234375</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>8342.8056640625</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>8249.0673828125</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>8272.5009765625</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>8202.197265625</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>8202.197265625</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>8155.32666015625</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>8131.892578125</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>8483.4150390625</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>8647.458984375</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>8624.0244140625</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>8670.89453125</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>8717.763671875</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>8741.1982421875</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>8741.1982421875</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>8788.068359375</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>8811.5029296875</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>8811.5029296875</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>8834.9384765625</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>8764.6328125</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>8881.806640625</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>8975.5478515625</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>8975.5478515625</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>9022.416015625</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>8952.1123046875</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>8975.5478515625</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>9092.7216796875</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>9116.15625</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>9092.7216796875</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>9139.5908203125</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>9069.287109375</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>9022.416015625</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>9022.416015625</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>8998.9814453125</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>8928.6767578125</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>8905.2431640625</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>8764.6328125</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>8952.1123046875</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>9045.8515625</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>8952.1123046875</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>9092.7216796875</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>9092.7216796875</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>8975.5478515625</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>9022.416015625</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>9092.7216796875</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>9186.4599609375</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>9116.15625</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>9233.3310546875</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>9327.0693359375</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>9256.765625</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>9397.3740234375</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>9350.5048828125</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>9256.765625</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>9209.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>9186.4599609375</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>9256.765625</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>9373.939453125</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>9256.765625</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>9209.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>9139.5908203125</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>9186.4599609375</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>9327.0693359375</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>9491.11328125</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>9514.548828125</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>9373.939453125</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>9678.591796875</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>9514.548828125</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>9514.548828125</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>9537.9833984375</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>9491.11328125</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>9491.11328125</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>9467.6787109375</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>9637.900390625</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>9446.1015625</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>9494.05078125</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>9134.427734375</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>9446.1015625</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>9422.126953125</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>9086.478515625</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>9134.427734375</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>9086.478515625</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>9086.478515625</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>8966.603515625</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>9326.228515625</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>9542.001953125</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>9374.1767578125</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>9230.3271484375</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>9398.1513671875</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>9398.1513671875</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>9158.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>9446.1015625</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>9398.1513671875</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>9302.2529296875</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>8990.5791015625</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>9134.427734375</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>9158.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>9110.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>9206.3525390625</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>9350.201171875</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>9086.478515625</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>8990.5791015625</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>9038.529296875</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>8918.654296875</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>8918.654296875</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>8774.8056640625</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>8630.9560546875</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>8870.705078125</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>8894.6796875</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>8966.603515625</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>9062.50390625</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>9086.478515625</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>8942.62890625</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>9134.427734375</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>8918.654296875</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>8870.705078125</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>8822.7548828125</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>8822.7548828125</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>8678.9052734375</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>9038.529296875</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>9206.3525390625</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>9206.3525390625</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>9206.3525390625</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>9110.4541015625</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>9350.201171875</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>9518.0263671875</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>9470.0771484375</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>9494.05078125</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>9589.951171875</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>9422.126953125</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>9542.001953125</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>9637.900390625</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>9685.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>9637.900390625</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>9542.001953125</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>9398.1513671875</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>9685.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>9709.8251953125</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>9685.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>9757.775390625</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>9877.6484375</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>9829.69921875</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>9757.775390625</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>9853.6748046875</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>9949.57421875</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>9781.75</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>9470.0771484375</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>9589.951171875</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>9685.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>9805.7255859375</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>9733.80078125</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>9781.75</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>9877.6484375</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>9781.75</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>9805.7255859375</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>9949.57421875</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>9997.5244140625</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>9997.5244140625</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>9781.75</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>9925.5986328125</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>9805.7255859375</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>9853.6748046875</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>9757.775390625</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>9877.6484375</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>9829.69921875</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>9877.6484375</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>9853.6748046875</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>9925.5986328125</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>9997.5244140625</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>10045.4736328125</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>9997.5244140625</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>10189.3232421875</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>10453.046875</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>10333.171875</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>10500.9970703125</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>10357.146484375</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>10405.09765625</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>10261.248046875</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>10213.2978515625</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>9901.6240234375</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>10117.3984375</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>10021.4990234375</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>10045.4736328125</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>9877.6484375</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>9973.5498046875</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>9997.5244140625</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>9949.57421875</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>10189.3232421875</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>10045.4736328125</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>10285.22265625</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>10309.1962890625</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>10237.2734375</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>10213.2978515625</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>10261.248046875</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>10309.1962890625</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>10165.34765625</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>9925.5986328125</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>9829.69921875</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>9997.5244140625</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>9949.57421875</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>10069.4482421875</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>10021.4990234375</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>9757.775390625</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>9637.900390625</c:v>
+                </c:pt>
+                <c:pt idx="937">
+                  <c:v>9733.80078125</c:v>
+                </c:pt>
+                <c:pt idx="938">
+                  <c:v>9733.80078125</c:v>
+                </c:pt>
+                <c:pt idx="939">
+                  <c:v>9685.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="940">
+                  <c:v>9757.775390625</c:v>
+                </c:pt>
+                <c:pt idx="941">
+                  <c:v>9589.951171875</c:v>
+                </c:pt>
+                <c:pt idx="942">
+                  <c:v>9518.0263671875</c:v>
+                </c:pt>
+                <c:pt idx="943">
+                  <c:v>9661.875</c:v>
+                </c:pt>
+                <c:pt idx="944">
+                  <c:v>9493.21484375</c:v>
+                </c:pt>
+                <c:pt idx="945">
+                  <c:v>9493.21484375</c:v>
+                </c:pt>
+                <c:pt idx="946">
+                  <c:v>9806.4423828125</c:v>
+                </c:pt>
+                <c:pt idx="947">
+                  <c:v>9637.78125</c:v>
+                </c:pt>
+                <c:pt idx="948">
+                  <c:v>9637.78125</c:v>
+                </c:pt>
+                <c:pt idx="949">
+                  <c:v>9637.78125</c:v>
+                </c:pt>
+                <c:pt idx="950">
+                  <c:v>9396.8359375</c:v>
+                </c:pt>
+                <c:pt idx="951">
+                  <c:v>9830.537109375</c:v>
+                </c:pt>
+                <c:pt idx="952">
+                  <c:v>9830.537109375</c:v>
+                </c:pt>
+                <c:pt idx="953">
+                  <c:v>9878.7255859375</c:v>
+                </c:pt>
+                <c:pt idx="954">
+                  <c:v>9710.064453125</c:v>
+                </c:pt>
+                <c:pt idx="955">
+                  <c:v>9975.103515625</c:v>
+                </c:pt>
+                <c:pt idx="956">
+                  <c:v>9975.103515625</c:v>
+                </c:pt>
+                <c:pt idx="957">
+                  <c:v>10047.3876953125</c:v>
+                </c:pt>
+                <c:pt idx="958">
+                  <c:v>9806.4423828125</c:v>
+                </c:pt>
+                <c:pt idx="959">
+                  <c:v>9685.9697265625</c:v>
+                </c:pt>
+                <c:pt idx="960">
+                  <c:v>9734.1591796875</c:v>
+                </c:pt>
+                <c:pt idx="961">
+                  <c:v>9541.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="962">
+                  <c:v>9445.025390625</c:v>
+                </c:pt>
+                <c:pt idx="963">
+                  <c:v>9324.5537109375</c:v>
+                </c:pt>
+                <c:pt idx="964">
+                  <c:v>9300.458984375</c:v>
+                </c:pt>
+                <c:pt idx="965">
+                  <c:v>9420.9306640625</c:v>
+                </c:pt>
+                <c:pt idx="966">
+                  <c:v>9396.8359375</c:v>
+                </c:pt>
+                <c:pt idx="967">
+                  <c:v>9445.025390625</c:v>
+                </c:pt>
+                <c:pt idx="968">
+                  <c:v>9324.5537109375</c:v>
+                </c:pt>
+                <c:pt idx="969">
+                  <c:v>9541.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="970">
+                  <c:v>9493.21484375</c:v>
+                </c:pt>
+                <c:pt idx="971">
+                  <c:v>9324.5537109375</c:v>
+                </c:pt>
+                <c:pt idx="972">
+                  <c:v>9179.986328125</c:v>
+                </c:pt>
+                <c:pt idx="973">
+                  <c:v>9324.5537109375</c:v>
+                </c:pt>
+                <c:pt idx="974">
+                  <c:v>9493.21484375</c:v>
+                </c:pt>
+                <c:pt idx="975">
+                  <c:v>9372.7431640625</c:v>
+                </c:pt>
+                <c:pt idx="976">
+                  <c:v>9324.5537109375</c:v>
+                </c:pt>
+                <c:pt idx="977">
+                  <c:v>9179.986328125</c:v>
+                </c:pt>
+                <c:pt idx="978">
+                  <c:v>9445.025390625</c:v>
+                </c:pt>
+                <c:pt idx="979">
+                  <c:v>9396.8359375</c:v>
+                </c:pt>
+                <c:pt idx="980">
+                  <c:v>9541.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="981">
+                  <c:v>9276.3642578125</c:v>
+                </c:pt>
+                <c:pt idx="982">
+                  <c:v>9228.17578125</c:v>
+                </c:pt>
+                <c:pt idx="983">
+                  <c:v>9252.26953125</c:v>
+                </c:pt>
+                <c:pt idx="984">
+                  <c:v>9252.26953125</c:v>
+                </c:pt>
+                <c:pt idx="985">
+                  <c:v>9011.3251953125</c:v>
+                </c:pt>
+                <c:pt idx="986">
+                  <c:v>8818.5703125</c:v>
+                </c:pt>
+                <c:pt idx="987">
+                  <c:v>9107.7041015625</c:v>
+                </c:pt>
+                <c:pt idx="988">
+                  <c:v>9011.3251953125</c:v>
+                </c:pt>
+                <c:pt idx="989">
+                  <c:v>8842.6650390625</c:v>
+                </c:pt>
+                <c:pt idx="990">
+                  <c:v>8794.4755859375</c:v>
+                </c:pt>
+                <c:pt idx="991">
+                  <c:v>8625.814453125</c:v>
+                </c:pt>
+                <c:pt idx="992">
+                  <c:v>9011.3251953125</c:v>
+                </c:pt>
+                <c:pt idx="993">
+                  <c:v>8818.5703125</c:v>
+                </c:pt>
+                <c:pt idx="994">
+                  <c:v>8746.2861328125</c:v>
+                </c:pt>
+                <c:pt idx="995">
+                  <c:v>8818.5703125</c:v>
+                </c:pt>
+                <c:pt idx="996">
+                  <c:v>8674.00390625</c:v>
+                </c:pt>
+                <c:pt idx="997">
+                  <c:v>8649.9091796875</c:v>
+                </c:pt>
+                <c:pt idx="998">
+                  <c:v>8987.23046875</c:v>
+                </c:pt>
+                <c:pt idx="999">
+                  <c:v>8963.13671875</c:v>
+                </c:pt>
+                <c:pt idx="1000">
+                  <c:v>8625.814453125</c:v>
+                </c:pt>
+                <c:pt idx="1001">
+                  <c:v>8674.00390625</c:v>
+                </c:pt>
+                <c:pt idx="1002">
+                  <c:v>8674.00390625</c:v>
+                </c:pt>
+                <c:pt idx="1003">
+                  <c:v>8601.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="1004">
+                  <c:v>8505.341796875</c:v>
+                </c:pt>
+                <c:pt idx="1005">
+                  <c:v>8457.15234375</c:v>
+                </c:pt>
+                <c:pt idx="1006">
+                  <c:v>8216.2080078125</c:v>
+                </c:pt>
+                <c:pt idx="1007">
+                  <c:v>8119.8310546875</c:v>
+                </c:pt>
+                <c:pt idx="1008">
+                  <c:v>8481.2470703125</c:v>
+                </c:pt>
+                <c:pt idx="1009">
+                  <c:v>8529.4365234375</c:v>
+                </c:pt>
+                <c:pt idx="1010">
+                  <c:v>8674.00390625</c:v>
+                </c:pt>
+                <c:pt idx="1011">
+                  <c:v>8649.9091796875</c:v>
+                </c:pt>
+                <c:pt idx="1012">
+                  <c:v>8601.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="1013">
+                  <c:v>8601.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="1014">
+                  <c:v>8601.7197265625</c:v>
+                </c:pt>
+                <c:pt idx="1015">
+                  <c:v>8794.4755859375</c:v>
+                </c:pt>
+                <c:pt idx="1016">
+                  <c:v>8649.9091796875</c:v>
+                </c:pt>
+                <c:pt idx="1017">
+                  <c:v>8433.0595703125</c:v>
+                </c:pt>
+                <c:pt idx="1018">
+                  <c:v>8288.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1019">
+                  <c:v>7999.3583984375</c:v>
+                </c:pt>
+                <c:pt idx="1020">
+                  <c:v>8023.453125</c:v>
+                </c:pt>
+                <c:pt idx="1021">
+                  <c:v>8071.6416015625</c:v>
+                </c:pt>
+                <c:pt idx="1022">
+                  <c:v>7848.119140625</c:v>
+                </c:pt>
+                <c:pt idx="1023">
+                  <c:v>7897.791015625</c:v>
+                </c:pt>
+                <c:pt idx="1024">
+                  <c:v>7997.13427734375</c:v>
+                </c:pt>
+                <c:pt idx="1025">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1026">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1027">
+                  <c:v>7723.93994140625</c:v>
+                </c:pt>
+                <c:pt idx="1028">
+                  <c:v>7872.955078125</c:v>
+                </c:pt>
+                <c:pt idx="1029">
+                  <c:v>8170.98486328125</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>8220.65625</c:v>
+                </c:pt>
+                <c:pt idx="1031">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1032">
+                  <c:v>8518.6865234375</c:v>
+                </c:pt>
+                <c:pt idx="1033">
+                  <c:v>8419.3427734375</c:v>
+                </c:pt>
+                <c:pt idx="1034">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1035">
+                  <c:v>8245.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1037">
+                  <c:v>8667.701171875</c:v>
+                </c:pt>
+                <c:pt idx="1038">
+                  <c:v>8419.3427734375</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>8543.5224609375</c:v>
+                </c:pt>
+                <c:pt idx="1040">
+                  <c:v>8717.373046875</c:v>
+                </c:pt>
+                <c:pt idx="1041">
+                  <c:v>8667.701171875</c:v>
+                </c:pt>
+                <c:pt idx="1042">
+                  <c:v>8767.044921875</c:v>
+                </c:pt>
+                <c:pt idx="1043">
+                  <c:v>8916.0595703125</c:v>
+                </c:pt>
+                <c:pt idx="1044">
+                  <c:v>8916.0595703125</c:v>
+                </c:pt>
+                <c:pt idx="1045">
+                  <c:v>8965.7314453125</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>9015.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>8916.0595703125</c:v>
+                </c:pt>
+                <c:pt idx="1048">
+                  <c:v>8940.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="1049">
+                  <c:v>9214.08984375</c:v>
+                </c:pt>
+                <c:pt idx="1050">
+                  <c:v>9214.08984375</c:v>
+                </c:pt>
+                <c:pt idx="1051">
+                  <c:v>9238.9248046875</c:v>
+                </c:pt>
+                <c:pt idx="1052">
+                  <c:v>9437.611328125</c:v>
+                </c:pt>
+                <c:pt idx="1053">
+                  <c:v>9412.7763671875</c:v>
+                </c:pt>
+                <c:pt idx="1054">
+                  <c:v>9636.298828125</c:v>
+                </c:pt>
+                <c:pt idx="1055">
+                  <c:v>9586.626953125</c:v>
+                </c:pt>
+                <c:pt idx="1056">
+                  <c:v>9611.462890625</c:v>
+                </c:pt>
+                <c:pt idx="1057">
+                  <c:v>9561.791015625</c:v>
+                </c:pt>
+                <c:pt idx="1058">
+                  <c:v>9387.9404296875</c:v>
+                </c:pt>
+                <c:pt idx="1059">
+                  <c:v>9338.2685546875</c:v>
+                </c:pt>
+                <c:pt idx="1060">
+                  <c:v>9040.23828125</c:v>
+                </c:pt>
+                <c:pt idx="1061">
+                  <c:v>8990.5673828125</c:v>
+                </c:pt>
+                <c:pt idx="1062">
+                  <c:v>8916.0595703125</c:v>
+                </c:pt>
+                <c:pt idx="1063">
+                  <c:v>8866.3876953125</c:v>
+                </c:pt>
+                <c:pt idx="1064">
+                  <c:v>9040.23828125</c:v>
+                </c:pt>
+                <c:pt idx="1065">
+                  <c:v>8990.5673828125</c:v>
+                </c:pt>
+                <c:pt idx="1066">
+                  <c:v>9065.07421875</c:v>
+                </c:pt>
+                <c:pt idx="1067">
+                  <c:v>8965.7314453125</c:v>
+                </c:pt>
+                <c:pt idx="1068">
+                  <c:v>8866.3876953125</c:v>
+                </c:pt>
+                <c:pt idx="1069">
+                  <c:v>9015.4033203125</c:v>
+                </c:pt>
+                <c:pt idx="1070">
+                  <c:v>8841.5517578125</c:v>
+                </c:pt>
+                <c:pt idx="1071">
+                  <c:v>8717.373046875</c:v>
+                </c:pt>
+                <c:pt idx="1072">
+                  <c:v>8642.865234375</c:v>
+                </c:pt>
+                <c:pt idx="1073">
+                  <c:v>8568.3583984375</c:v>
+                </c:pt>
+                <c:pt idx="1074">
+                  <c:v>8717.373046875</c:v>
+                </c:pt>
+                <c:pt idx="1075">
+                  <c:v>8543.5224609375</c:v>
+                </c:pt>
+                <c:pt idx="1076">
+                  <c:v>8593.1943359375</c:v>
+                </c:pt>
+                <c:pt idx="1077">
+                  <c:v>8618.029296875</c:v>
+                </c:pt>
+                <c:pt idx="1078">
+                  <c:v>8642.865234375</c:v>
+                </c:pt>
+                <c:pt idx="1079">
+                  <c:v>8618.029296875</c:v>
+                </c:pt>
+                <c:pt idx="1080">
+                  <c:v>8543.5224609375</c:v>
+                </c:pt>
+                <c:pt idx="1081">
+                  <c:v>8593.1943359375</c:v>
+                </c:pt>
+                <c:pt idx="1082">
+                  <c:v>8568.3583984375</c:v>
+                </c:pt>
+                <c:pt idx="1083">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1084">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1085">
+                  <c:v>8543.5224609375</c:v>
+                </c:pt>
+                <c:pt idx="1086">
+                  <c:v>8568.3583984375</c:v>
+                </c:pt>
+                <c:pt idx="1087">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1088">
+                  <c:v>8493.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="1089">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1090">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1091">
+                  <c:v>8369.671875</c:v>
+                </c:pt>
+                <c:pt idx="1092">
+                  <c:v>8394.5078125</c:v>
+                </c:pt>
+                <c:pt idx="1093">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1094">
+                  <c:v>8369.671875</c:v>
+                </c:pt>
+                <c:pt idx="1095">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1096">
+                  <c:v>8394.5078125</c:v>
+                </c:pt>
+                <c:pt idx="1097">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1098">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1099">
+                  <c:v>8320</c:v>
+                </c:pt>
+                <c:pt idx="1100">
+                  <c:v>8220.65625</c:v>
+                </c:pt>
+                <c:pt idx="1101">
+                  <c:v>8245.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1102">
+                  <c:v>8220.65625</c:v>
+                </c:pt>
+                <c:pt idx="1103">
+                  <c:v>8369.671875</c:v>
+                </c:pt>
+                <c:pt idx="1104">
+                  <c:v>8245.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1105">
+                  <c:v>8245.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1106">
+                  <c:v>8245.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1107">
+                  <c:v>8493.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="1108">
+                  <c:v>8791.880859375</c:v>
+                </c:pt>
+                <c:pt idx="1109">
+                  <c:v>8866.3876953125</c:v>
+                </c:pt>
+                <c:pt idx="1110">
+                  <c:v>8717.373046875</c:v>
+                </c:pt>
+                <c:pt idx="1111">
+                  <c:v>8642.865234375</c:v>
+                </c:pt>
+                <c:pt idx="1112">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1113">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1114">
+                  <c:v>8493.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="1115">
+                  <c:v>8394.5078125</c:v>
+                </c:pt>
+                <c:pt idx="1116">
+                  <c:v>8419.3427734375</c:v>
+                </c:pt>
+                <c:pt idx="1117">
+                  <c:v>8195.8203125</c:v>
+                </c:pt>
+                <c:pt idx="1118">
+                  <c:v>8245.4921875</c:v>
+                </c:pt>
+                <c:pt idx="1119">
+                  <c:v>8270.328125</c:v>
+                </c:pt>
+                <c:pt idx="1120">
+                  <c:v>8021.97021484375</c:v>
+                </c:pt>
+                <c:pt idx="1121">
+                  <c:v>7947.46240234375</c:v>
+                </c:pt>
+                <c:pt idx="1122">
+                  <c:v>7947.46240234375</c:v>
+                </c:pt>
+                <c:pt idx="1123">
+                  <c:v>7922.626953125</c:v>
+                </c:pt>
+                <c:pt idx="1124">
+                  <c:v>7947.46240234375</c:v>
+                </c:pt>
+                <c:pt idx="1125">
+                  <c:v>7649.4326171875</c:v>
+                </c:pt>
+                <c:pt idx="1126">
+                  <c:v>7475.58203125</c:v>
+                </c:pt>
+                <c:pt idx="1127">
+                  <c:v>7748.77587890625</c:v>
+                </c:pt>
+                <c:pt idx="1128">
+                  <c:v>7798.44775390625</c:v>
+                </c:pt>
+                <c:pt idx="1129">
+                  <c:v>7872.955078125</c:v>
+                </c:pt>
+                <c:pt idx="1130">
+                  <c:v>7972.29833984375</c:v>
+                </c:pt>
+                <c:pt idx="1131">
+                  <c:v>7872.955078125</c:v>
+                </c:pt>
+                <c:pt idx="1132">
+                  <c:v>7798.44775390625</c:v>
+                </c:pt>
+                <c:pt idx="1133">
+                  <c:v>7649.4326171875</c:v>
+                </c:pt>
+                <c:pt idx="1134">
+                  <c:v>7748.77587890625</c:v>
+                </c:pt>
+                <c:pt idx="1135">
+                  <c:v>7674.2685546875</c:v>
+                </c:pt>
+                <c:pt idx="1136">
+                  <c:v>7823.28369140625</c:v>
+                </c:pt>
+                <c:pt idx="1137">
+                  <c:v>7723.93994140625</c:v>
+                </c:pt>
+                <c:pt idx="1138">
+                  <c:v>7649.4326171875</c:v>
+                </c:pt>
+                <c:pt idx="1139">
+                  <c:v>7574.92529296875</c:v>
+                </c:pt>
+                <c:pt idx="1140">
+                  <c:v>7723.93994140625</c:v>
+                </c:pt>
+                <c:pt idx="1141">
+                  <c:v>7574.92529296875</c:v>
+                </c:pt>
+                <c:pt idx="1142">
+                  <c:v>7450.74609375</c:v>
+                </c:pt>
+                <c:pt idx="1143">
+                  <c:v>7450.74609375</c:v>
+                </c:pt>
+                <c:pt idx="1144">
+                  <c:v>7475.58203125</c:v>
+                </c:pt>
+                <c:pt idx="1145">
+                  <c:v>7450.74609375</c:v>
+                </c:pt>
+                <c:pt idx="1146">
+                  <c:v>7525.25341796875</c:v>
+                </c:pt>
+                <c:pt idx="1147">
+                  <c:v>7326.56689453125</c:v>
+                </c:pt>
+                <c:pt idx="1148">
+                  <c:v>7500.41796875</c:v>
+                </c:pt>
+                <c:pt idx="1149">
+                  <c:v>7351.40283203125</c:v>
+                </c:pt>
+                <c:pt idx="1150">
+                  <c:v>7276.8955078125</c:v>
+                </c:pt>
+                <c:pt idx="1151">
+                  <c:v>7202.38818359375</c:v>
+                </c:pt>
+                <c:pt idx="1152">
+                  <c:v>7202.38818359375</c:v>
+                </c:pt>
+                <c:pt idx="1153">
+                  <c:v>7252.0595703125</c:v>
+                </c:pt>
+                <c:pt idx="1154">
+                  <c:v>7450.74609375</c:v>
+                </c:pt>
+                <c:pt idx="1155">
+                  <c:v>7823.28369140625</c:v>
+                </c:pt>
+                <c:pt idx="1156">
+                  <c:v>8419.3427734375</c:v>
+                </c:pt>
+                <c:pt idx="1157">
+                  <c:v>8146.14892578125</c:v>
+                </c:pt>
+                <c:pt idx="1158">
+                  <c:v>8270.328125</c:v>
+                </c:pt>
+                <c:pt idx="1159">
+                  <c:v>8220.65625</c:v>
+                </c:pt>
+                <c:pt idx="1160">
+                  <c:v>8295.1640625</c:v>
+                </c:pt>
+                <c:pt idx="1161">
+                  <c:v>8220.65625</c:v>
+                </c:pt>
+                <c:pt idx="1162">
+                  <c:v>8543.5224609375</c:v>
+                </c:pt>
+                <c:pt idx="1163">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1164">
+                  <c:v>8469.0146484375</c:v>
+                </c:pt>
+                <c:pt idx="1165">
+                  <c:v>8593.1943359375</c:v>
+                </c:pt>
+                <c:pt idx="1166">
+                  <c:v>8593.1943359375</c:v>
+                </c:pt>
+                <c:pt idx="1167">
+                  <c:v>8642.865234375</c:v>
+                </c:pt>
+                <c:pt idx="1168">
+                  <c:v>8493.8505859375</c:v>
+                </c:pt>
+                <c:pt idx="1169">
+                  <c:v>8618.029296875</c:v>
+                </c:pt>
+                <c:pt idx="1170">
+                  <c:v>8518.6865234375</c:v>
+                </c:pt>
+                <c:pt idx="1171">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1172">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1173">
+                  <c:v>8320</c:v>
+                </c:pt>
+                <c:pt idx="1174">
+                  <c:v>8369.671875</c:v>
+                </c:pt>
+                <c:pt idx="1175">
+                  <c:v>8518.6865234375</c:v>
+                </c:pt>
+                <c:pt idx="1176">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1177">
+                  <c:v>8419.3427734375</c:v>
+                </c:pt>
+                <c:pt idx="1178">
+                  <c:v>8369.671875</c:v>
+                </c:pt>
+                <c:pt idx="1179">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1180">
+                  <c:v>8419.3427734375</c:v>
+                </c:pt>
+                <c:pt idx="1181">
+                  <c:v>8444.1787109375</c:v>
+                </c:pt>
+                <c:pt idx="1182">
+                  <c:v>8369.671875</c:v>
+                </c:pt>
+                <c:pt idx="1183">
+                  <c:v>8270.328125</c:v>
+                </c:pt>
+                <c:pt idx="1184">
+                  <c:v>8220.65625</c:v>
+                </c:pt>
+                <c:pt idx="1185">
+                  <c:v>8344.8359375</c:v>
+                </c:pt>
+                <c:pt idx="1186">
+                  <c:v>8320</c:v>
+                </c:pt>
+                <c:pt idx="1187">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="1188">
+                  <c:v>8225</c:v>
+                </c:pt>
+                <c:pt idx="1189">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="1190">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="1191">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="1192">
+                  <c:v>8075</c:v>
+                </c:pt>
+                <c:pt idx="1193">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="1194">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="1195">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="1196">
+                  <c:v>8075</c:v>
+                </c:pt>
+                <c:pt idx="1197">
+                  <c:v>8025</c:v>
+                </c:pt>
+                <c:pt idx="1198">
+                  <c:v>8175</c:v>
+                </c:pt>
+                <c:pt idx="1199">
+                  <c:v>8050</c:v>
+                </c:pt>
+                <c:pt idx="1200">
+                  <c:v>8175</c:v>
+                </c:pt>
+                <c:pt idx="1201">
+                  <c:v>8025</c:v>
+                </c:pt>
+                <c:pt idx="1202">
+                  <c:v>8025</c:v>
+                </c:pt>
+                <c:pt idx="1203">
+                  <c:v>8025</c:v>
+                </c:pt>
+                <c:pt idx="1204">
+                  <c:v>8075</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$1206</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1205"/>
+                <c:pt idx="0">
+                  <c:v>47937000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>104831000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>89753500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71360000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75033500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>169034500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>95235000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>76581500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>89319500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89853500</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>86343000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73777000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>107216000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>66428000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>80829000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>76836500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>98658000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97920000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>104627000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>132762500</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>113129000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>86741000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>67291000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>80950500</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>51602000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45604000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>75574000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44984500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>36926000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>83922000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>47221000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>66011500</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>91204000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>70487500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>68913000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>58360000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>71869000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>78688000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>173631500</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>205539000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>81446500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>84470000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>120802500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>111871500</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>90883000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>135582000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>50302000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>74328000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>57416000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>70755500</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>71474500</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>70067500</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>125853000</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>67523500</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>127762500</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>152050000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>119101500</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>134467500</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>113370500</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>83115500</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>223390500</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>112286000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>73311500</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>80215000</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>107908000</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>123697500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>116961000</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>110411500</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>119211500</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>135519500</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>102686500</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>79293500</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>47095000</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>72721000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>68397000</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>63758000</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>108498500</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>108742000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>132650000</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>87660000</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>57355000</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>65829500</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>42065500</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>50123500</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>51685000</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>38115500</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>48864000</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>68180500</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>70680000</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>129058500</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>73563000</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>64912500</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>64950000</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>92620000</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>59210000</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>87470000</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>537971500</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>102108500</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>101442000</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>141732500</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>133810500</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>62108500</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>62576000</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>64348000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>77198000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>73262500</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>72780500</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>61478500</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>87799000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>48984000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>68448500</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>118043000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>60823500</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>65824000</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>52451000</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>56010000</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>68939500</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>84420500</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>53704000</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>65795000</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>58153000</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>67392500</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>39710500</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>34279500</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>35595000</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>47297000</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>40707500</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>65981500</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>65946500</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>59321000</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>49724000</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>47998500</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>47119000</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>55009500</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>60792000</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>79938000</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>48171500</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>53107500</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>74133000</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>84605000</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>105685000</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>119981500</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>110071500</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>41112000</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>93768000</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>67285000</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>52858500</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>60446000</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>118325500</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>86929000</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>69282000</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>186354500</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>100926000</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>120163500</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>68253000</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>59561500</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>80751500</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>74337000</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>71572500</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>74564500</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>115373500</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>67362500</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>53257000</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>35764500</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>36780000</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>53902000</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>77888000</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>110074000</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>41483500</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>29929000</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>51990500</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>44514000</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>58672500</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>117540000</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>73157500</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>57115500</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>68722000</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>60998500</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>60539500</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>55052500</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>80186000</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>74079000</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>156848000</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>103954500</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>74719000</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>54986500</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>174312000</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>107263500</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>94643500</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>47201000</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>91067000</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>210893300</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>138811900</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>142378200</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>116644300</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>134601200</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>106120100</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>96730700</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>60329800</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>70103000</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>57067000</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>75271900</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>60639200</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>38593400</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>90535400</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>61621500</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>61081400</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>43120400</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>85441700</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>101785800</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>47503900</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>55790000</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>52590100</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>67344200</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>98616900</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>61968100</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>78839600</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>68203700</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>66328300</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>43477500</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>35181400</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>40216100</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>113288400</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>87907900</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>144923700</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>76538100</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>66831000</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>63283700</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>56944100</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>51258200</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>74775000</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>54886400</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>91092400</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>59977100</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>49763600</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>52477600</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>95171400</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>107096800</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>74753000</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>52386100</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>33232000</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>37136400</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>30802100</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>20722100</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>39343800</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>42079500</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>49954700</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>54287400</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>70624000</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>76164900</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>63657100</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>143433300</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>45351900</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>110334600</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>62606000</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>50025200</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>65898700</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>63902600</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>71476300</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>60389700</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>59925500</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>63370500</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>40278300</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>106796900</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>53350200</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>71945100</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>70595000</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>68122000</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>65308100</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>35100600</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>39324700</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>56813200</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>61883100</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>108922200</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>93277000</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>71968800</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>57710700</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>55617000</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>77055100</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>48704600</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>56813400</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>43821700</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>80095500</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>99240300</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>124947700</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>135899900</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>136616800</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>100301000</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>132983400</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>130990900</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>119256500</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>132814500</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>86484000</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>61053900</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>78432100</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>111214500</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>149761300</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>132439400</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>143981700</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>85485500</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>60010900</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>82208000</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>95245100</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>85101200</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>83911500</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>62180600</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>71430600</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>112691900</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>105575400</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>57321200</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>48528300</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>119263000</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>68619400</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>69791600</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>62776200</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>73471300</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>57622100</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>93342900</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>68464700</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>98632000</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>124388800</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>129323400</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>85956100</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>91279600</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>128360900</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>89463100</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>133730600</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>456796600</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>268445700</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>156535200</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>240529600</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>212968600</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>159657600</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>153514300</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>140908900</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>86520200</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>71603500</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>108710800</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>76747400</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>84336900</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>105411400</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>286292700</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>149226300</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>80563100</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>81140300</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>129242500</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>108910500</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>107828300</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>111768600</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>85539500</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>80865100</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>130367100</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>132666300</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>117839400</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>88138700</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>44295700</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>53041800</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>60443000</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>57956600</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>76354100</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>146078100</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>98517800</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>101343900</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>68738800</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>102238600</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>69172900</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>66801100</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>86126800</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>64312400</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>36830800</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>34269000</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>71988200</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>83316300</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>57419900</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>60077700</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>59641000</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>105792900</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>64337100</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>38956500</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>31247600</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>44379900</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>58465500</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>86909700</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>131553000</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>104841600</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>106466900</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>60170600</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>164221000</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>118734200</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>84328900</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>92875800</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>104376300</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>73204700</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>59381200</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>81411000</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>83556700</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>86136900</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>58194900</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>97293300</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>71671800</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>108892400</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>99503500</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>80472400</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>57762100</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>124467000</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>137659900</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>74960800</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>71430600</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>62906000</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>67079900</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>117931700</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>132777400</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>91234600</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>52395300</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>124485200</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>116642400</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>190404800</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>363127600</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>102530600</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>89238400</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>90933700</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>61908500</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>60567600</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>106228200</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>89567100</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>89153400</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>62643700</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>176524800</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>115079600</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>80524500</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>63788000</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>43967400</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>112043400</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>80238200</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>64060000</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>47569700</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>62282800</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>70642900</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>56387500</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>85665300</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>66753500</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>91812300</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>122777800</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>89416500</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>84696300</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>98962100</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>77003400</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>84980600</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>138922800</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>118118400</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>68323600</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>81856300</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>84458300</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>94794000</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>42525500</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>96599500</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>89463000</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>59597900</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>49208200</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>59092900</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>143424800</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>72679800</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>83556900</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>35901000</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>84684200</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>84642100</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>53520800</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>75048300</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>96209700</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>91562100</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>644359600</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>155775400</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>130982100</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>114656300</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>180553800</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>229308700</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>172590100</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>90851300</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>102851800</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>104580200</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>118164300</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>113255700</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>181516700</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>67482900</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>41243700</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>33617700</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>59591500</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>47393000</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>20495900</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>27193800</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>40420200</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>47020900</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>44681400</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>10653900</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>27399100</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>90918800</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>128838500</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>69286600</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>86916900</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>101759100</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>96069100</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>103804600</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>119748200</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>105710700</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>88695900</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>96814600</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>66391800</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>96859500</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>42474500</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>66124500</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>77582300</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>196804700</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>68544300</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>200589000</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>77396200</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>99109500</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>71716700</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>117757700</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>116014700</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>54495500</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>72381700</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>62060900</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>63775000</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>81678200</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>38037000</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>66040400</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>43588900</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>40077000</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>25390500</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>38671900</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>53412300</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>44123400</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>59983900</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>106349400</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>67034700</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>56672000</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>95376900</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>92652000</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>106115600</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>79350900</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>54201400</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>59580100</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>82077700</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>90495300</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>86747400</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>105894000</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>198558600</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>37277900</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>91617400</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>145603600</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>110692800</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>98296600</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>101068200</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>118912100</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>97146900</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>60288900</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>60975800</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>36922100</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>45489400</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>32996000</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>44554300</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>91903600</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>51726500</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>110354200</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>83946900</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>91178700</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>186928200</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>54842400</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>145775300</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>83645900</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>83728800</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>67565000</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>64815100</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>84754500</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>40929600</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>45322600</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>81993900</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>96525600</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>64830300</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>49497000</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>69996100</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>123592500</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>91000000</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>102980500</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>77392900</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>76325700</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>55675900</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>79148200</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>97189500</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>722827900</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>163535600</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>74872200</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>87492200</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>53188400</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>44632400</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>38082300</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>45552600</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>72223700</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>59073000</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>112769400</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>32330600</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>54990100</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>42676300</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>48291100</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>47813500</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>36389900</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>36225100</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>108855900</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>35049300</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>44609200</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>52532400</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>37641300</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>28981500</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>43703500</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>61566500</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>65230900</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>55554500</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>62550100</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>52924600</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>83476600</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>42667800</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>62061200</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>122802700</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>113868700</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>77848400</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>74510200</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>80868000</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>49756400</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>60629900</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>64596100</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>52675900</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>55589300</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>43373400</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>77056800</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>76738100</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>68898600</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>75495400</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>59303700</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>53440000</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>79328900</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>73573000</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>65664600</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>63749800</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>53725900</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>50379000</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>44423100</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>45428500</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>56227000</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>136107200</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>42152700</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>40610600</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>42007200</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>49318400</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>61405200</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>80732300</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>53155900</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>66479000</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>69490200</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>112757900</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>121005300</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>34272200</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>33325800</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>54305500</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>40607000</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>42445300</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>56132200</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>73544700</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>84345000</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>118960000</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>93663000</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>98380200</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>112582800</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>72855700</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>53344400</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>43774500</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>71966100</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>84305800</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>71064500</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>62941800</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>29429200</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>59606000</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>50919200</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>89509700</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>64554500</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>50633500</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>76963200</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>54748400</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>63199400</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>52450700</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>51958200</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>64907600</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>67027600</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>56050900</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>60414100</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>84994200</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>60648200</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>31829300</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>46076800</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>50754600</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>20827700</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>37195700</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>84977900</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>48714300</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>57050500</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>49216000</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>107614800</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>40364800</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>55542100</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>43631900</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>35679000</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>69070600</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>54715600</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>205312100</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>80566400</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>54747400</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>94363900</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>81852800</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>91322500</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>43891600</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>78642800</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>87589300</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>51560500</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>115332800</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>275013500</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>111712200</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>65174500</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>72938100</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>88116700</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>64449600</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>64464700</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>70184600</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>79903400</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>30545200</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>34603300</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>56501800</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>85290100</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>50896000</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>59848600</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>52774900</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>39381500</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>68253400</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>88399500</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>44869200</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>107706100</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>71048900</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>63176500</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>52868300</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>92348600</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>84906000</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>63212700</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>78977300</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>73452800</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>73136400</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>102581200</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>104208700</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>99324000</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>57983300</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>87651000</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>92953500</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>87949400</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>66072400</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>164748900</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>142277200</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>53341300</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>63997700</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>75371600</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>66913000</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>55192300</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>41356000</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>43735800</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>54043100</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>126671200</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>51520600</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>43822900</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>61952900</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>70242200</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>118369300</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>100947200</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>141622600</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>110681100</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>154176800</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>62444100</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>55004800</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>66269700</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>90279400</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>91968200</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>66971000</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>65742700</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>39514100</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>79229700</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>79248700</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>76763100</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>177418400</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>75993500</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>70428600</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>283265900</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>95620700</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>127134000</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>147784300</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>128908000</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>178833000</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>132832700</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>104874100</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>100932900</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>90063500</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>109623000</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>97079400</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>81200400</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>53076200</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>66746800</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>112808900</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>145469900</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>95363500</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>54741900</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>61126000</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>99848500</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>87890100</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>75311400</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>121712700</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>128578500</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>73945700</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>117351600</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>207115100</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>756431600</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>72197700</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>75353100</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>82087300</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>44991300</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>51599800</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>45584700</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>68690900</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>49785700</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>84652200</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>52986300</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>100051000</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>81474800</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>166841200</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>79592300</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>80029000</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>77913200</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>89150700</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>166172300</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>68634600</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>78848500</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>55860200</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>67054000</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>36946900</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>72903600</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>61853200</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>62325900</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>55908400</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>62646500</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>36682600</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>37192700</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>90666000</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>65383200</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>53880300</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>31285300</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>39321100</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>24658000</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>98088100</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>75565800</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>69092500</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>32122900</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>82519900</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>61176200</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>55699900</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>126328300</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>78473900</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>52327400</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>54162100</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>47062400</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>40364100</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>55207100</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>47999100</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>33396600</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>40731400</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>51054400</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>60304400</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>84848800</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>56611600</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>46651600</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>35145600</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>60448400</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>38489900</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>53004700</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>158403700</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>72008600</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>50950200</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>44817000</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>39332900</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>31541800</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>36185100</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>55093100</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>64621300</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>70759100</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>70057100</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>89745000</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>65420200</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>140886600</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>142194600</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>72553800</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>105191100</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>158369100</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>84960100</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>93027400</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>144692100</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>59797700</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>86746200</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>60887000</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>58500400</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>91867900</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>99622900</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>56835200</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>51080000</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>44632100</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>31738600</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>66635200</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>63255900</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>66993300</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>56299600</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>36472500</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>94799500</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>48903000</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>85341200</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>34847500</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>39061500</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>49680100</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>114484100</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>97553400</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>47710000</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>49275700</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>50296500</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>50324900</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>131579100</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>92166100</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>128707600</c:v>
+                </c:pt>
+                <c:pt idx="937">
+                  <c:v>80378500</c:v>
+                </c:pt>
+                <c:pt idx="938">
+                  <c:v>62933100</c:v>
+                </c:pt>
+                <c:pt idx="939">
+                  <c:v>56381400</c:v>
+                </c:pt>
+                <c:pt idx="940">
+                  <c:v>63598200</c:v>
+                </c:pt>
+                <c:pt idx="941">
+                  <c:v>65716200</c:v>
+                </c:pt>
+                <c:pt idx="942">
+                  <c:v>85295300</c:v>
+                </c:pt>
+                <c:pt idx="943">
+                  <c:v>58584400</c:v>
+                </c:pt>
+                <c:pt idx="944">
+                  <c:v>93181200</c:v>
+                </c:pt>
+                <c:pt idx="945">
+                  <c:v>58396100</c:v>
+                </c:pt>
+                <c:pt idx="946">
+                  <c:v>165369400</c:v>
+                </c:pt>
+                <c:pt idx="947">
+                  <c:v>62310100</c:v>
+                </c:pt>
+                <c:pt idx="948">
+                  <c:v>57443500</c:v>
+                </c:pt>
+                <c:pt idx="949">
+                  <c:v>76886000</c:v>
+                </c:pt>
+                <c:pt idx="950">
+                  <c:v>87879600</c:v>
+                </c:pt>
+                <c:pt idx="951">
+                  <c:v>126087100</c:v>
+                </c:pt>
+                <c:pt idx="952">
+                  <c:v>97876300</c:v>
+                </c:pt>
+                <c:pt idx="953">
+                  <c:v>96904400</c:v>
+                </c:pt>
+                <c:pt idx="954">
+                  <c:v>68247200</c:v>
+                </c:pt>
+                <c:pt idx="955">
+                  <c:v>64458400</c:v>
+                </c:pt>
+                <c:pt idx="956">
+                  <c:v>61230400</c:v>
+                </c:pt>
+                <c:pt idx="957">
+                  <c:v>37934300</c:v>
+                </c:pt>
+                <c:pt idx="958">
+                  <c:v>44780100</c:v>
+                </c:pt>
+                <c:pt idx="959">
+                  <c:v>75126400</c:v>
+                </c:pt>
+                <c:pt idx="960">
+                  <c:v>57746100</c:v>
+                </c:pt>
+                <c:pt idx="961">
+                  <c:v>99845900</c:v>
+                </c:pt>
+                <c:pt idx="962">
+                  <c:v>84868500</c:v>
+                </c:pt>
+                <c:pt idx="963">
+                  <c:v>104254100</c:v>
+                </c:pt>
+                <c:pt idx="964">
+                  <c:v>91576900</c:v>
+                </c:pt>
+                <c:pt idx="965">
+                  <c:v>43292100</c:v>
+                </c:pt>
+                <c:pt idx="966">
+                  <c:v>32415700</c:v>
+                </c:pt>
+                <c:pt idx="967">
+                  <c:v>24016700</c:v>
+                </c:pt>
+                <c:pt idx="968">
+                  <c:v>56350100</c:v>
+                </c:pt>
+                <c:pt idx="969">
+                  <c:v>38124800</c:v>
+                </c:pt>
+                <c:pt idx="970">
+                  <c:v>41916000</c:v>
+                </c:pt>
+                <c:pt idx="971">
+                  <c:v>41593900</c:v>
+                </c:pt>
+                <c:pt idx="972">
+                  <c:v>71318600</c:v>
+                </c:pt>
+                <c:pt idx="973">
+                  <c:v>55943100</c:v>
+                </c:pt>
+                <c:pt idx="974">
+                  <c:v>42733800</c:v>
+                </c:pt>
+                <c:pt idx="975">
+                  <c:v>72531300</c:v>
+                </c:pt>
+                <c:pt idx="976">
+                  <c:v>88270100</c:v>
+                </c:pt>
+                <c:pt idx="977">
+                  <c:v>70942600</c:v>
+                </c:pt>
+                <c:pt idx="978">
+                  <c:v>77098000</c:v>
+                </c:pt>
+                <c:pt idx="979">
+                  <c:v>76979000</c:v>
+                </c:pt>
+                <c:pt idx="980">
+                  <c:v>71033100</c:v>
+                </c:pt>
+                <c:pt idx="981">
+                  <c:v>112111200</c:v>
+                </c:pt>
+                <c:pt idx="982">
+                  <c:v>124547900</c:v>
+                </c:pt>
+                <c:pt idx="983">
+                  <c:v>90154800</c:v>
+                </c:pt>
+                <c:pt idx="984">
+                  <c:v>120515400</c:v>
+                </c:pt>
+                <c:pt idx="985">
+                  <c:v>152057000</c:v>
+                </c:pt>
+                <c:pt idx="986">
+                  <c:v>154645800</c:v>
+                </c:pt>
+                <c:pt idx="987">
+                  <c:v>112982800</c:v>
+                </c:pt>
+                <c:pt idx="988">
+                  <c:v>90439900</c:v>
+                </c:pt>
+                <c:pt idx="989">
+                  <c:v>94607700</c:v>
+                </c:pt>
+                <c:pt idx="990">
+                  <c:v>98229900</c:v>
+                </c:pt>
+                <c:pt idx="991">
+                  <c:v>171477800</c:v>
+                </c:pt>
+                <c:pt idx="992">
+                  <c:v>131162200</c:v>
+                </c:pt>
+                <c:pt idx="993">
+                  <c:v>76209100</c:v>
+                </c:pt>
+                <c:pt idx="994">
+                  <c:v>71188300</c:v>
+                </c:pt>
+                <c:pt idx="995">
+                  <c:v>121172600</c:v>
+                </c:pt>
+                <c:pt idx="996">
+                  <c:v>90439700</c:v>
+                </c:pt>
+                <c:pt idx="997">
+                  <c:v>116274500</c:v>
+                </c:pt>
+                <c:pt idx="998">
+                  <c:v>89096400</c:v>
+                </c:pt>
+                <c:pt idx="999">
+                  <c:v>107318300</c:v>
+                </c:pt>
+                <c:pt idx="1000">
+                  <c:v>154438200</c:v>
+                </c:pt>
+                <c:pt idx="1001">
+                  <c:v>119260800</c:v>
+                </c:pt>
+                <c:pt idx="1002">
+                  <c:v>106054700</c:v>
+                </c:pt>
+                <c:pt idx="1003">
+                  <c:v>108530300</c:v>
+                </c:pt>
+                <c:pt idx="1004">
+                  <c:v>101592700</c:v>
+                </c:pt>
+                <c:pt idx="1005">
+                  <c:v>117843500</c:v>
+                </c:pt>
+                <c:pt idx="1006">
+                  <c:v>199991600</c:v>
+                </c:pt>
+                <c:pt idx="1007">
+                  <c:v>293095000</c:v>
+                </c:pt>
+                <c:pt idx="1008">
+                  <c:v>192944300</c:v>
+                </c:pt>
+                <c:pt idx="1009">
+                  <c:v>125418500</c:v>
+                </c:pt>
+                <c:pt idx="1010">
+                  <c:v>155207900</c:v>
+                </c:pt>
+                <c:pt idx="1011">
+                  <c:v>96270100</c:v>
+                </c:pt>
+                <c:pt idx="1012">
+                  <c:v>82295300</c:v>
+                </c:pt>
+                <c:pt idx="1013">
+                  <c:v>97652100</c:v>
+                </c:pt>
+                <c:pt idx="1014">
+                  <c:v>109295600</c:v>
+                </c:pt>
+                <c:pt idx="1015">
+                  <c:v>87968900</c:v>
+                </c:pt>
+                <c:pt idx="1016">
+                  <c:v>83030700</c:v>
+                </c:pt>
+                <c:pt idx="1017">
+                  <c:v>111397800</c:v>
+                </c:pt>
+                <c:pt idx="1018">
+                  <c:v>151365700</c:v>
+                </c:pt>
+                <c:pt idx="1019">
+                  <c:v>417305700</c:v>
+                </c:pt>
+                <c:pt idx="1020">
+                  <c:v>214108200</c:v>
+                </c:pt>
+                <c:pt idx="1021">
+                  <c:v>152917300</c:v>
+                </c:pt>
+                <c:pt idx="1022">
+                  <c:v>377916400</c:v>
+                </c:pt>
+                <c:pt idx="1023">
+                  <c:v>331836800</c:v>
+                </c:pt>
+                <c:pt idx="1024">
+                  <c:v>136341700</c:v>
+                </c:pt>
+                <c:pt idx="1025">
+                  <c:v>283104600</c:v>
+                </c:pt>
+                <c:pt idx="1026">
+                  <c:v>122943900</c:v>
+                </c:pt>
+                <c:pt idx="1027">
+                  <c:v>533073600</c:v>
+                </c:pt>
+                <c:pt idx="1028">
+                  <c:v>136753900</c:v>
+                </c:pt>
+                <c:pt idx="1029">
+                  <c:v>144148600</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>82603000</c:v>
+                </c:pt>
+                <c:pt idx="1031">
+                  <c:v>83319300</c:v>
+                </c:pt>
+                <c:pt idx="1032">
+                  <c:v>83431800</c:v>
+                </c:pt>
+                <c:pt idx="1033">
+                  <c:v>76874900</c:v>
+                </c:pt>
+                <c:pt idx="1034">
+                  <c:v>83540600</c:v>
+                </c:pt>
+                <c:pt idx="1035">
+                  <c:v>40683800</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>56537100</c:v>
+                </c:pt>
+                <c:pt idx="1037">
+                  <c:v>92329600</c:v>
+                </c:pt>
+                <c:pt idx="1038">
+                  <c:v>143675300</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>58297000</c:v>
+                </c:pt>
+                <c:pt idx="1040">
+                  <c:v>73235400</c:v>
+                </c:pt>
+                <c:pt idx="1041">
+                  <c:v>60315700</c:v>
+                </c:pt>
+                <c:pt idx="1042">
+                  <c:v>164597500</c:v>
+                </c:pt>
+                <c:pt idx="1043">
+                  <c:v>92219000</c:v>
+                </c:pt>
+                <c:pt idx="1044">
+                  <c:v>86385600</c:v>
+                </c:pt>
+                <c:pt idx="1045">
+                  <c:v>48860500</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>77382000</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>99614500</c:v>
+                </c:pt>
+                <c:pt idx="1048">
+                  <c:v>47167500</c:v>
+                </c:pt>
+                <c:pt idx="1049">
+                  <c:v>149002900</c:v>
+                </c:pt>
+                <c:pt idx="1050">
+                  <c:v>101401300</c:v>
+                </c:pt>
+                <c:pt idx="1051">
+                  <c:v>63007500</c:v>
+                </c:pt>
+                <c:pt idx="1052">
+                  <c:v>111597200</c:v>
+                </c:pt>
+                <c:pt idx="1053">
+                  <c:v>160614800</c:v>
+                </c:pt>
+                <c:pt idx="1054">
+                  <c:v>169739200</c:v>
+                </c:pt>
+                <c:pt idx="1055">
+                  <c:v>103113000</c:v>
+                </c:pt>
+                <c:pt idx="1056">
+                  <c:v>48521800</c:v>
+                </c:pt>
+                <c:pt idx="1057">
+                  <c:v>56625300</c:v>
+                </c:pt>
+                <c:pt idx="1058">
+                  <c:v>93212000</c:v>
+                </c:pt>
+                <c:pt idx="1059">
+                  <c:v>236950800</c:v>
+                </c:pt>
+                <c:pt idx="1060">
+                  <c:v>264428700</c:v>
+                </c:pt>
+                <c:pt idx="1061">
+                  <c:v>128318100</c:v>
+                </c:pt>
+                <c:pt idx="1062">
+                  <c:v>93357200</c:v>
+                </c:pt>
+                <c:pt idx="1063">
+                  <c:v>95529000</c:v>
+                </c:pt>
+                <c:pt idx="1064">
+                  <c:v>80406400</c:v>
+                </c:pt>
+                <c:pt idx="1065">
+                  <c:v>56632600</c:v>
+                </c:pt>
+                <c:pt idx="1066">
+                  <c:v>41337300</c:v>
+                </c:pt>
+                <c:pt idx="1067">
+                  <c:v>83318000</c:v>
+                </c:pt>
+                <c:pt idx="1068">
+                  <c:v>57825000</c:v>
+                </c:pt>
+                <c:pt idx="1069">
+                  <c:v>54927900</c:v>
+                </c:pt>
+                <c:pt idx="1070">
+                  <c:v>86270200</c:v>
+                </c:pt>
+                <c:pt idx="1071">
+                  <c:v>78879500</c:v>
+                </c:pt>
+                <c:pt idx="1072">
+                  <c:v>445915100</c:v>
+                </c:pt>
+                <c:pt idx="1073">
+                  <c:v>87324500</c:v>
+                </c:pt>
+                <c:pt idx="1074">
+                  <c:v>110158900</c:v>
+                </c:pt>
+                <c:pt idx="1075">
+                  <c:v>117561000</c:v>
+                </c:pt>
+                <c:pt idx="1076">
+                  <c:v>117281700</c:v>
+                </c:pt>
+                <c:pt idx="1077">
+                  <c:v>185441800</c:v>
+                </c:pt>
+                <c:pt idx="1078">
+                  <c:v>82364500</c:v>
+                </c:pt>
+                <c:pt idx="1079">
+                  <c:v>68545100</c:v>
+                </c:pt>
+                <c:pt idx="1080">
+                  <c:v>50370800</c:v>
+                </c:pt>
+                <c:pt idx="1081">
+                  <c:v>43593300</c:v>
+                </c:pt>
+                <c:pt idx="1082">
+                  <c:v>49936900</c:v>
+                </c:pt>
+                <c:pt idx="1083">
+                  <c:v>215611000</c:v>
+                </c:pt>
+                <c:pt idx="1084">
+                  <c:v>94459300</c:v>
+                </c:pt>
+                <c:pt idx="1085">
+                  <c:v>111769400</c:v>
+                </c:pt>
+                <c:pt idx="1086">
+                  <c:v>135986500</c:v>
+                </c:pt>
+                <c:pt idx="1087">
+                  <c:v>125196000</c:v>
+                </c:pt>
+                <c:pt idx="1088">
+                  <c:v>77219300</c:v>
+                </c:pt>
+                <c:pt idx="1089">
+                  <c:v>97475300</c:v>
+                </c:pt>
+                <c:pt idx="1090">
+                  <c:v>86016400</c:v>
+                </c:pt>
+                <c:pt idx="1091">
+                  <c:v>80432200</c:v>
+                </c:pt>
+                <c:pt idx="1092">
+                  <c:v>95383500</c:v>
+                </c:pt>
+                <c:pt idx="1093">
+                  <c:v>77981700</c:v>
+                </c:pt>
+                <c:pt idx="1094">
+                  <c:v>70969500</c:v>
+                </c:pt>
+                <c:pt idx="1095">
+                  <c:v>138256800</c:v>
+                </c:pt>
+                <c:pt idx="1096">
+                  <c:v>58682800</c:v>
+                </c:pt>
+                <c:pt idx="1097">
+                  <c:v>99484300</c:v>
+                </c:pt>
+                <c:pt idx="1098">
+                  <c:v>104240300</c:v>
+                </c:pt>
+                <c:pt idx="1099">
+                  <c:v>98098100</c:v>
+                </c:pt>
+                <c:pt idx="1100">
+                  <c:v>206006300</c:v>
+                </c:pt>
+                <c:pt idx="1101">
+                  <c:v>86196100</c:v>
+                </c:pt>
+                <c:pt idx="1102">
+                  <c:v>49054500</c:v>
+                </c:pt>
+                <c:pt idx="1103">
+                  <c:v>69475900</c:v>
+                </c:pt>
+                <c:pt idx="1104">
+                  <c:v>56325400</c:v>
+                </c:pt>
+                <c:pt idx="1105">
+                  <c:v>43621300</c:v>
+                </c:pt>
+                <c:pt idx="1106">
+                  <c:v>68378700</c:v>
+                </c:pt>
+                <c:pt idx="1107">
+                  <c:v>128561300</c:v>
+                </c:pt>
+                <c:pt idx="1108">
+                  <c:v>171015700</c:v>
+                </c:pt>
+                <c:pt idx="1109">
+                  <c:v>129083900</c:v>
+                </c:pt>
+                <c:pt idx="1110">
+                  <c:v>122930900</c:v>
+                </c:pt>
+                <c:pt idx="1111">
+                  <c:v>68754200</c:v>
+                </c:pt>
+                <c:pt idx="1112">
+                  <c:v>128591700</c:v>
+                </c:pt>
+                <c:pt idx="1113">
+                  <c:v>202260200</c:v>
+                </c:pt>
+                <c:pt idx="1114">
+                  <c:v>69470200</c:v>
+                </c:pt>
+                <c:pt idx="1115">
+                  <c:v>66394100</c:v>
+                </c:pt>
+                <c:pt idx="1116">
+                  <c:v>64052700</c:v>
+                </c:pt>
+                <c:pt idx="1117">
+                  <c:v>326794200</c:v>
+                </c:pt>
+                <c:pt idx="1118">
+                  <c:v>111915700</c:v>
+                </c:pt>
+                <c:pt idx="1119">
+                  <c:v>81281400</c:v>
+                </c:pt>
+                <c:pt idx="1120">
+                  <c:v>236499300</c:v>
+                </c:pt>
+                <c:pt idx="1121">
+                  <c:v>421127500</c:v>
+                </c:pt>
+                <c:pt idx="1122">
+                  <c:v>155531500</c:v>
+                </c:pt>
+                <c:pt idx="1123">
+                  <c:v>212372700</c:v>
+                </c:pt>
+                <c:pt idx="1124">
+                  <c:v>103534800</c:v>
+                </c:pt>
+                <c:pt idx="1125">
+                  <c:v>321191900</c:v>
+                </c:pt>
+                <c:pt idx="1126">
+                  <c:v>595368700</c:v>
+                </c:pt>
+                <c:pt idx="1127">
+                  <c:v>246849600</c:v>
+                </c:pt>
+                <c:pt idx="1128">
+                  <c:v>235173400</c:v>
+                </c:pt>
+                <c:pt idx="1129">
+                  <c:v>156084700</c:v>
+                </c:pt>
+                <c:pt idx="1130">
+                  <c:v>142567700</c:v>
+                </c:pt>
+                <c:pt idx="1131">
+                  <c:v>129312900</c:v>
+                </c:pt>
+                <c:pt idx="1132">
+                  <c:v>183725900</c:v>
+                </c:pt>
+                <c:pt idx="1133">
+                  <c:v>275378700</c:v>
+                </c:pt>
+                <c:pt idx="1134">
+                  <c:v>149025300</c:v>
+                </c:pt>
+                <c:pt idx="1135">
+                  <c:v>92588800</c:v>
+                </c:pt>
+                <c:pt idx="1136">
+                  <c:v>102606200</c:v>
+                </c:pt>
+                <c:pt idx="1137">
+                  <c:v>150428400</c:v>
+                </c:pt>
+                <c:pt idx="1138">
+                  <c:v>147986600</c:v>
+                </c:pt>
+                <c:pt idx="1139">
+                  <c:v>121657700</c:v>
+                </c:pt>
+                <c:pt idx="1140">
+                  <c:v>116454700</c:v>
+                </c:pt>
+                <c:pt idx="1141">
+                  <c:v>170666700</c:v>
+                </c:pt>
+                <c:pt idx="1142">
+                  <c:v>202433400</c:v>
+                </c:pt>
+                <c:pt idx="1143">
+                  <c:v>126952400</c:v>
+                </c:pt>
+                <c:pt idx="1144">
+                  <c:v>76787500</c:v>
+                </c:pt>
+                <c:pt idx="1145">
+                  <c:v>104032400</c:v>
+                </c:pt>
+                <c:pt idx="1146">
+                  <c:v>74282600</c:v>
+                </c:pt>
+                <c:pt idx="1147">
+                  <c:v>168080800</c:v>
+                </c:pt>
+                <c:pt idx="1148">
+                  <c:v>293567400</c:v>
+                </c:pt>
+                <c:pt idx="1149">
+                  <c:v>107426000</c:v>
+                </c:pt>
+                <c:pt idx="1150">
+                  <c:v>101847900</c:v>
+                </c:pt>
+                <c:pt idx="1151">
+                  <c:v>151862300</c:v>
+                </c:pt>
+                <c:pt idx="1152">
+                  <c:v>133206400</c:v>
+                </c:pt>
+                <c:pt idx="1153">
+                  <c:v>120611200</c:v>
+                </c:pt>
+                <c:pt idx="1154">
+                  <c:v>157334400</c:v>
+                </c:pt>
+                <c:pt idx="1155">
+                  <c:v>393421800</c:v>
+                </c:pt>
+                <c:pt idx="1156">
+                  <c:v>529802600</c:v>
+                </c:pt>
+                <c:pt idx="1157">
+                  <c:v>392957200</c:v>
+                </c:pt>
+                <c:pt idx="1158">
+                  <c:v>187003900</c:v>
+                </c:pt>
+                <c:pt idx="1159">
+                  <c:v>133355100</c:v>
+                </c:pt>
+                <c:pt idx="1160">
+                  <c:v>182275600</c:v>
+                </c:pt>
+                <c:pt idx="1161">
+                  <c:v>180270000</c:v>
+                </c:pt>
+                <c:pt idx="1162">
+                  <c:v>239156800</c:v>
+                </c:pt>
+                <c:pt idx="1163">
+                  <c:v>259009800</c:v>
+                </c:pt>
+                <c:pt idx="1164">
+                  <c:v>177088000</c:v>
+                </c:pt>
+                <c:pt idx="1165">
+                  <c:v>115007100</c:v>
+                </c:pt>
+                <c:pt idx="1166">
+                  <c:v>155231500</c:v>
+                </c:pt>
+                <c:pt idx="1167">
+                  <c:v>125731500</c:v>
+                </c:pt>
+                <c:pt idx="1168">
+                  <c:v>89756900</c:v>
+                </c:pt>
+                <c:pt idx="1169">
+                  <c:v>75241900</c:v>
+                </c:pt>
+                <c:pt idx="1170">
+                  <c:v>79897700</c:v>
+                </c:pt>
+                <c:pt idx="1171">
+                  <c:v>130897600</c:v>
+                </c:pt>
+                <c:pt idx="1172">
+                  <c:v>85415600</c:v>
+                </c:pt>
+                <c:pt idx="1173">
+                  <c:v>104113800</c:v>
+                </c:pt>
+                <c:pt idx="1174">
+                  <c:v>89815300</c:v>
+                </c:pt>
+                <c:pt idx="1175">
+                  <c:v>129411100</c:v>
+                </c:pt>
+                <c:pt idx="1176">
+                  <c:v>119377900</c:v>
+                </c:pt>
+                <c:pt idx="1177">
+                  <c:v>114209700</c:v>
+                </c:pt>
+                <c:pt idx="1178">
+                  <c:v>124087400</c:v>
+                </c:pt>
+                <c:pt idx="1179">
+                  <c:v>103917100</c:v>
+                </c:pt>
+                <c:pt idx="1180">
+                  <c:v>279590600</c:v>
+                </c:pt>
+                <c:pt idx="1181">
+                  <c:v>98807700</c:v>
+                </c:pt>
+                <c:pt idx="1182">
+                  <c:v>77094400</c:v>
+                </c:pt>
+                <c:pt idx="1183">
+                  <c:v>71051300</c:v>
+                </c:pt>
+                <c:pt idx="1184">
+                  <c:v>67559300</c:v>
+                </c:pt>
+                <c:pt idx="1185">
+                  <c:v>76359200</c:v>
+                </c:pt>
+                <c:pt idx="1186">
+                  <c:v>97044000</c:v>
+                </c:pt>
+                <c:pt idx="1187">
+                  <c:v>103550900</c:v>
+                </c:pt>
+                <c:pt idx="1188">
+                  <c:v>71410400</c:v>
+                </c:pt>
+                <c:pt idx="1189">
+                  <c:v>71162300</c:v>
+                </c:pt>
+                <c:pt idx="1190">
+                  <c:v>61745200</c:v>
+                </c:pt>
+                <c:pt idx="1191">
+                  <c:v>113057200</c:v>
+                </c:pt>
+                <c:pt idx="1192">
+                  <c:v>143418300</c:v>
+                </c:pt>
+                <c:pt idx="1193">
+                  <c:v>140766000</c:v>
+                </c:pt>
+                <c:pt idx="1194">
+                  <c:v>100006800</c:v>
+                </c:pt>
+                <c:pt idx="1195">
+                  <c:v>143105700</c:v>
+                </c:pt>
+                <c:pt idx="1196">
+                  <c:v>122332000</c:v>
+                </c:pt>
+                <c:pt idx="1197">
+                  <c:v>89802700</c:v>
+                </c:pt>
+                <c:pt idx="1198">
+                  <c:v>88497200</c:v>
+                </c:pt>
+                <c:pt idx="1199">
+                  <c:v>131069800</c:v>
+                </c:pt>
+                <c:pt idx="1200">
+                  <c:v>72424200</c:v>
+                </c:pt>
+                <c:pt idx="1201">
+                  <c:v>85044100</c:v>
+                </c:pt>
+                <c:pt idx="1202">
+                  <c:v>71260500</c:v>
+                </c:pt>
+                <c:pt idx="1203">
+                  <c:v>78399400</c:v>
+                </c:pt>
+                <c:pt idx="1204">
+                  <c:v>101995600</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B0FD-4094-B6B3-485874CD3879}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="763045983"/>
+        <c:axId val="763044543"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="763045983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="763044543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="763044543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="763045983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1328,7 +8896,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1986,7 +9554,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2764,6 +10332,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3405,7 +11013,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3432,8 +11040,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3534,7 +11142,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -3566,10 +11174,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3609,22 +11217,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3729,8 +11338,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3862,19 +11471,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3888,6 +11498,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -4913,6 +12534,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4946,6 +13070,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>166008</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4710BA1-454B-2DEE-FC0B-6DF8D2AE01ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
